--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/60.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/60.xlsx
@@ -426,13 +426,13 @@
         <v>-5.80323010862969</v>
       </c>
       <c r="E2">
-        <v>-26.70325853906774</v>
+        <v>-23.21045106542561</v>
       </c>
       <c r="F2">
-        <v>-6.204431463945328</v>
+        <v>-6.987320250257185</v>
       </c>
       <c r="G2">
-        <v>-17.58752261896196</v>
+        <v>-13.81733762647282</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.705557248218166</v>
       </c>
       <c r="E3">
-        <v>-28.50240314841914</v>
+        <v>-25.16002705283781</v>
       </c>
       <c r="F3">
-        <v>-5.861742051285921</v>
+        <v>-6.361327625281998</v>
       </c>
       <c r="G3">
-        <v>-17.32010833720902</v>
+        <v>-11.92033213210519</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.665806087167637</v>
       </c>
       <c r="E4">
-        <v>-29.30274300216477</v>
+        <v>-23.72397096094741</v>
       </c>
       <c r="F4">
-        <v>-5.686248431384245</v>
+        <v>-7.027650509173287</v>
       </c>
       <c r="G4">
-        <v>-16.72503777652502</v>
+        <v>-12.30192547423482</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.676830984957295</v>
       </c>
       <c r="E5">
-        <v>-29.34561406559538</v>
+        <v>-22.78638211697731</v>
       </c>
       <c r="F5">
-        <v>-5.65865314766067</v>
+        <v>-6.630487155993467</v>
       </c>
       <c r="G5">
-        <v>-17.35698946978927</v>
+        <v>-13.18253058768095</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.714720463910512</v>
       </c>
       <c r="E6">
-        <v>-30.22270928953401</v>
+        <v>-22.83015434673545</v>
       </c>
       <c r="F6">
-        <v>-5.958826391314189</v>
+        <v>-7.015141608000189</v>
       </c>
       <c r="G6">
-        <v>-17.70702007074749</v>
+        <v>-13.37875655343018</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.750182798731323</v>
       </c>
       <c r="E7">
-        <v>-29.95836414781026</v>
+        <v>-23.2089702544251</v>
       </c>
       <c r="F7">
-        <v>-5.691221267958724</v>
+        <v>-5.495884604789549</v>
       </c>
       <c r="G7">
-        <v>-16.39108980579658</v>
+        <v>-13.12365584581056</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.761284858299718</v>
       </c>
       <c r="E8">
-        <v>-30.23127716235652</v>
+        <v>-25.67457944043336</v>
       </c>
       <c r="F8">
-        <v>-5.61459603279906</v>
+        <v>-5.966887454423777</v>
       </c>
       <c r="G8">
-        <v>-16.76552409319754</v>
+        <v>-13.00313212490785</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.729512277234893</v>
       </c>
       <c r="E9">
-        <v>-30.44490339519437</v>
+        <v>-26.06401009119698</v>
       </c>
       <c r="F9">
-        <v>-5.560580575141167</v>
+        <v>-6.279847539638554</v>
       </c>
       <c r="G9">
-        <v>-16.2839754496007</v>
+        <v>-14.47295972034286</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.635116122816132</v>
       </c>
       <c r="E10">
-        <v>-30.88144149682278</v>
+        <v>-26.96139967140099</v>
       </c>
       <c r="F10">
-        <v>-5.552986705276634</v>
+        <v>-5.941008116059581</v>
       </c>
       <c r="G10">
-        <v>-16.39485886189305</v>
+        <v>-13.70392992320678</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.478038889892116</v>
       </c>
       <c r="E11">
-        <v>-31.00789460501296</v>
+        <v>-27.3253214280794</v>
       </c>
       <c r="F11">
-        <v>-5.384363993489092</v>
+        <v>-5.710870307251581</v>
       </c>
       <c r="G11">
-        <v>-16.86031494362349</v>
+        <v>-14.27252108539491</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.264108803273392</v>
       </c>
       <c r="E12">
-        <v>-31.72350671007507</v>
+        <v>-26.11685285439249</v>
       </c>
       <c r="F12">
-        <v>-5.313916795105557</v>
+        <v>-5.556340202552578</v>
       </c>
       <c r="G12">
-        <v>-16.80193678358399</v>
+        <v>-14.66602411510208</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.001683784520658</v>
       </c>
       <c r="E13">
-        <v>-32.76953892110685</v>
+        <v>-26.84117321497135</v>
       </c>
       <c r="F13">
-        <v>-5.318842120502574</v>
+        <v>-5.530283489125853</v>
       </c>
       <c r="G13">
-        <v>-15.32869767097076</v>
+        <v>-13.74456024861025</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.718125383773655</v>
       </c>
       <c r="E14">
-        <v>-33.06192437388609</v>
+        <v>-27.7469766998816</v>
       </c>
       <c r="F14">
-        <v>-5.280160103517965</v>
+        <v>-5.422360265812316</v>
       </c>
       <c r="G14">
-        <v>-15.08930881248052</v>
+        <v>-12.38882067354961</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.439029217665039</v>
       </c>
       <c r="E15">
-        <v>-33.22730650888322</v>
+        <v>-26.61699110922162</v>
       </c>
       <c r="F15">
-        <v>-5.178415708833516</v>
+        <v>-5.337095123030971</v>
       </c>
       <c r="G15">
-        <v>-15.18870794229714</v>
+        <v>-13.96705539321359</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.184410333293399</v>
       </c>
       <c r="E16">
-        <v>-33.79282007872408</v>
+        <v>-27.25918306519737</v>
       </c>
       <c r="F16">
-        <v>-5.505146908835997</v>
+        <v>-4.880072437365286</v>
       </c>
       <c r="G16">
-        <v>-14.55450342279342</v>
+        <v>-13.12821777756367</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.983658013143061</v>
       </c>
       <c r="E17">
-        <v>-34.16746526185266</v>
+        <v>-28.5398672138846</v>
       </c>
       <c r="F17">
-        <v>-5.073174491487776</v>
+        <v>-4.08211904445929</v>
       </c>
       <c r="G17">
-        <v>-14.70302939314005</v>
+        <v>-12.12742992940537</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.853534560486275</v>
       </c>
       <c r="E18">
-        <v>-33.69643150947083</v>
+        <v>-29.07614721976896</v>
       </c>
       <c r="F18">
-        <v>-5.158107847879836</v>
+        <v>-4.594221438158043</v>
       </c>
       <c r="G18">
-        <v>-14.71692871858668</v>
+        <v>-11.36392543277434</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.798226099711139</v>
       </c>
       <c r="E19">
-        <v>-35.56908910162574</v>
+        <v>-29.41081050588381</v>
       </c>
       <c r="F19">
-        <v>-4.668588308682291</v>
+        <v>-4.252509172048462</v>
       </c>
       <c r="G19">
-        <v>-14.1341171080346</v>
+        <v>-10.95682102671908</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.828578527573788</v>
       </c>
       <c r="E20">
-        <v>-36.12475776897394</v>
+        <v>-31.00573905138531</v>
       </c>
       <c r="F20">
-        <v>-4.582142513140987</v>
+        <v>-4.003865759618554</v>
       </c>
       <c r="G20">
-        <v>-13.69347356512099</v>
+        <v>-10.32282838212988</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.940892735916447</v>
       </c>
       <c r="E21">
-        <v>-36.40520616426896</v>
+        <v>-27.98313661938161</v>
       </c>
       <c r="F21">
-        <v>-4.688855785135128</v>
+        <v>-3.558630597081485</v>
       </c>
       <c r="G21">
-        <v>-14.3553989376978</v>
+        <v>-10.77110935360259</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.124059906823787</v>
       </c>
       <c r="E22">
-        <v>-36.15614009384709</v>
+        <v>-28.3398399884918</v>
       </c>
       <c r="F22">
-        <v>-4.358052085371093</v>
+        <v>-3.773621842514221</v>
       </c>
       <c r="G22">
-        <v>-13.20068892996386</v>
+        <v>-11.13632211640391</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.373695681914355</v>
       </c>
       <c r="E23">
-        <v>-36.80047401802847</v>
+        <v>-31.10647269144894</v>
       </c>
       <c r="F23">
-        <v>-4.156119287064113</v>
+        <v>-3.76633996271503</v>
       </c>
       <c r="G23">
-        <v>-13.8591564377249</v>
+        <v>-10.2043307150972</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.672266062763694</v>
       </c>
       <c r="E24">
-        <v>-38.20223144778478</v>
+        <v>-33.863611448649</v>
       </c>
       <c r="F24">
-        <v>-3.840289526730559</v>
+        <v>-4.17307365074185</v>
       </c>
       <c r="G24">
-        <v>-13.5808206662379</v>
+        <v>-10.30749724573751</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.9987817797931</v>
       </c>
       <c r="E25">
-        <v>-38.26582027980048</v>
+        <v>-33.13265460941189</v>
       </c>
       <c r="F25">
-        <v>-3.644405693167601</v>
+        <v>-4.05050431512233</v>
       </c>
       <c r="G25">
-        <v>-13.80086435186941</v>
+        <v>-9.079900612138204</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.337314094884698</v>
       </c>
       <c r="E26">
-        <v>-37.4517478286266</v>
+        <v>-32.37270421534068</v>
       </c>
       <c r="F26">
-        <v>-3.880413507951176</v>
+        <v>-3.512091023197423</v>
       </c>
       <c r="G26">
-        <v>-13.63434060069853</v>
+        <v>-10.29460267086205</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.662631749210627</v>
       </c>
       <c r="E27">
-        <v>-37.76307135970593</v>
+        <v>-32.24859459244947</v>
       </c>
       <c r="F27">
-        <v>-3.885890754859723</v>
+        <v>-2.922370410730025</v>
       </c>
       <c r="G27">
-        <v>-13.51237182666793</v>
+        <v>-8.896337483076696</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.952419785753823</v>
       </c>
       <c r="E28">
-        <v>-37.02811134944604</v>
+        <v>-33.92325145133001</v>
       </c>
       <c r="F28">
-        <v>-3.594905381074625</v>
+        <v>-3.572058047685538</v>
       </c>
       <c r="G28">
-        <v>-13.55692349326267</v>
+        <v>-10.4789868152173</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.190187742848347</v>
       </c>
       <c r="E29">
-        <v>-37.78219284120331</v>
+        <v>-30.96994599282868</v>
       </c>
       <c r="F29">
-        <v>-4.017313798399508</v>
+        <v>-2.643699142290426</v>
       </c>
       <c r="G29">
-        <v>-14.04404047445657</v>
+        <v>-10.56961962044592</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.355540894549074</v>
       </c>
       <c r="E30">
-        <v>-38.33763734908813</v>
+        <v>-32.04854925316063</v>
       </c>
       <c r="F30">
-        <v>-3.852049335005655</v>
+        <v>-3.543594101267345</v>
       </c>
       <c r="G30">
-        <v>-13.45064173926991</v>
+        <v>-11.15296422882982</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.436541300239919</v>
       </c>
       <c r="E31">
-        <v>-37.12778985506588</v>
+        <v>-32.27539183738986</v>
       </c>
       <c r="F31">
-        <v>-4.1699450397059</v>
+        <v>-3.816699435267131</v>
       </c>
       <c r="G31">
-        <v>-14.10565138221518</v>
+        <v>-9.67542471756108</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.427203697747883</v>
       </c>
       <c r="E32">
-        <v>-37.57416833071296</v>
+        <v>-33.69188265733012</v>
       </c>
       <c r="F32">
-        <v>-4.099814582505452</v>
+        <v>-3.22323969313338</v>
       </c>
       <c r="G32">
-        <v>-14.17738593823288</v>
+        <v>-11.13651412804518</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.321224536322102</v>
       </c>
       <c r="E33">
-        <v>-37.43203311703421</v>
+        <v>-32.70183823469218</v>
       </c>
       <c r="F33">
-        <v>-4.203992341328975</v>
+        <v>-3.708765126012187</v>
       </c>
       <c r="G33">
-        <v>-14.17246646756152</v>
+        <v>-10.75572855902713</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.123839218983316</v>
       </c>
       <c r="E34">
-        <v>-37.1524202251936</v>
+        <v>-32.11146334254919</v>
       </c>
       <c r="F34">
-        <v>-3.798434554944368</v>
+        <v>-3.818439928068199</v>
       </c>
       <c r="G34">
-        <v>-14.01627492901871</v>
+        <v>-11.741559362439</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.843377704034617</v>
       </c>
       <c r="E35">
-        <v>-36.21053159515322</v>
+        <v>-32.62141706478996</v>
       </c>
       <c r="F35">
-        <v>-4.095838688804742</v>
+        <v>-3.524816892080937</v>
       </c>
       <c r="G35">
-        <v>-14.35807716903907</v>
+        <v>-10.26272542786441</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.487507759958156</v>
       </c>
       <c r="E36">
-        <v>-35.54611388874783</v>
+        <v>-32.03424606800741</v>
       </c>
       <c r="F36">
-        <v>-3.773272635359866</v>
+        <v>-3.516321101697562</v>
       </c>
       <c r="G36">
-        <v>-14.24517266869499</v>
+        <v>-11.04390161658407</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.074625571964734</v>
       </c>
       <c r="E37">
-        <v>-36.20740241961392</v>
+        <v>-30.82037502482934</v>
       </c>
       <c r="F37">
-        <v>-4.082446871583786</v>
+        <v>-3.608939391044292</v>
       </c>
       <c r="G37">
-        <v>-14.43007987924545</v>
+        <v>-11.97735958956467</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.619361084498303</v>
       </c>
       <c r="E38">
-        <v>-35.64701734658674</v>
+        <v>-32.17643335913724</v>
       </c>
       <c r="F38">
-        <v>-3.976181788363714</v>
+        <v>-3.382948516175871</v>
       </c>
       <c r="G38">
-        <v>-13.8029963431967</v>
+        <v>-10.51747190711133</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.133086184179342</v>
       </c>
       <c r="E39">
-        <v>-35.17173814982271</v>
+        <v>-30.61020401765935</v>
       </c>
       <c r="F39">
-        <v>-3.913513753436818</v>
+        <v>-3.615948873426027</v>
       </c>
       <c r="G39">
-        <v>-13.92546004378542</v>
+        <v>-10.33595138464755</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.635011844000447</v>
       </c>
       <c r="E40">
-        <v>-34.95064219910921</v>
+        <v>-33.02357952022614</v>
       </c>
       <c r="F40">
-        <v>-3.739213455942425</v>
+        <v>-3.608643238038105</v>
       </c>
       <c r="G40">
-        <v>-14.49950864029504</v>
+        <v>-9.638224117336289</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.135733759119272</v>
       </c>
       <c r="E41">
-        <v>-34.85669447734608</v>
+        <v>-33.24859033671927</v>
       </c>
       <c r="F41">
-        <v>-4.035331620599463</v>
+        <v>-3.345374301479113</v>
       </c>
       <c r="G41">
-        <v>-14.76295854376471</v>
+        <v>-11.38452033657414</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.644163414016809</v>
       </c>
       <c r="E42">
-        <v>-34.06335564441632</v>
+        <v>-29.38064181204471</v>
       </c>
       <c r="F42">
-        <v>-3.997435121748912</v>
+        <v>-3.277475285913519</v>
       </c>
       <c r="G42">
-        <v>-15.02540866248151</v>
+        <v>-10.18667888628181</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.173876576299521</v>
       </c>
       <c r="E43">
-        <v>-33.72474805744078</v>
+        <v>-29.5552099565664</v>
       </c>
       <c r="F43">
-        <v>-3.725169151884308</v>
+        <v>-3.000677541571886</v>
       </c>
       <c r="G43">
-        <v>-14.09400322773526</v>
+        <v>-11.06416215528441</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.730083174370956</v>
       </c>
       <c r="E44">
-        <v>-33.83981658197569</v>
+        <v>-30.59676350680459</v>
       </c>
       <c r="F44">
-        <v>-3.607453083042652</v>
+        <v>-2.988890810296228</v>
       </c>
       <c r="G44">
-        <v>-14.63606864378998</v>
+        <v>-9.014398158098185</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.318413105757867</v>
       </c>
       <c r="E45">
-        <v>-32.98719323157451</v>
+        <v>-29.65039848020763</v>
       </c>
       <c r="F45">
-        <v>-3.855059959950906</v>
+        <v>-3.041196657418404</v>
       </c>
       <c r="G45">
-        <v>-14.79197713068919</v>
+        <v>-9.314449453050029</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.9459500746792752</v>
       </c>
       <c r="E46">
-        <v>-32.81169448564425</v>
+        <v>-31.22496700657064</v>
       </c>
       <c r="F46">
-        <v>-3.575138355691068</v>
+        <v>-3.163609998005254</v>
       </c>
       <c r="G46">
-        <v>-14.28060212705627</v>
+        <v>-10.21485162882101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.6126439854426179</v>
       </c>
       <c r="E47">
-        <v>-32.57001209209189</v>
+        <v>-29.94832225669825</v>
       </c>
       <c r="F47">
-        <v>-3.660304516852697</v>
+        <v>-2.945330187239108</v>
       </c>
       <c r="G47">
-        <v>-14.85816652292861</v>
+        <v>-10.30788126902006</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.320178822353774</v>
       </c>
       <c r="E48">
-        <v>-32.3799158101979</v>
+        <v>-29.86994116433649</v>
       </c>
       <c r="F48">
-        <v>-3.609716990648772</v>
+        <v>-2.908566038118097</v>
       </c>
       <c r="G48">
-        <v>-14.62900062906364</v>
+        <v>-8.82636579255866</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.06940662551025528</v>
       </c>
       <c r="E49">
-        <v>-31.29962116482409</v>
+        <v>-27.77413848697961</v>
       </c>
       <c r="F49">
-        <v>-3.411365743269559</v>
+        <v>-3.533161438549387</v>
       </c>
       <c r="G49">
-        <v>-15.05876902988074</v>
+        <v>-10.00544638127995</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.1436423035823629</v>
       </c>
       <c r="E50">
-        <v>-31.38985327366393</v>
+        <v>-29.08252331117176</v>
       </c>
       <c r="F50">
-        <v>-3.627778364761402</v>
+        <v>-3.210434638954094</v>
       </c>
       <c r="G50">
-        <v>-15.02920916876059</v>
+        <v>-9.46093116152616</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.3198758448744045</v>
       </c>
       <c r="E51">
-        <v>-30.99451749279431</v>
+        <v>-28.96448863616183</v>
       </c>
       <c r="F51">
-        <v>-3.583380753127972</v>
+        <v>-2.70797622242741</v>
       </c>
       <c r="G51">
-        <v>-15.02004226816235</v>
+        <v>-8.906755769888782</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.4621590284949155</v>
       </c>
       <c r="E52">
-        <v>-30.50891563952979</v>
+        <v>-29.48067806711115</v>
       </c>
       <c r="F52">
-        <v>-3.601029571849629</v>
+        <v>-3.698588231799572</v>
       </c>
       <c r="G52">
-        <v>-15.40979776031906</v>
+        <v>-9.476566868108138</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.575619898362094</v>
       </c>
       <c r="E53">
-        <v>-30.67444947840617</v>
+        <v>-27.57816877429767</v>
       </c>
       <c r="F53">
-        <v>-3.798835232540974</v>
+        <v>-3.775131114251634</v>
       </c>
       <c r="G53">
-        <v>-15.01286500543321</v>
+        <v>-10.63921721931802</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.6621731098793336</v>
       </c>
       <c r="E54">
-        <v>-31.08990074081786</v>
+        <v>-27.98520613200311</v>
       </c>
       <c r="F54">
-        <v>-3.66711682784796</v>
+        <v>-2.432914219769098</v>
       </c>
       <c r="G54">
-        <v>-15.26002371430412</v>
+        <v>-9.907003999124179</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.7249653164709786</v>
       </c>
       <c r="E55">
-        <v>-29.81041437350567</v>
+        <v>-27.29499876612404</v>
       </c>
       <c r="F55">
-        <v>-3.920470973523343</v>
+        <v>-3.287619714154867</v>
       </c>
       <c r="G55">
-        <v>-14.67461498077648</v>
+        <v>-9.928022652753011</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.7672959026335293</v>
       </c>
       <c r="E56">
-        <v>-29.26190522356359</v>
+        <v>-26.29621665288829</v>
       </c>
       <c r="F56">
-        <v>-3.808756358248245</v>
+        <v>-3.898602370389998</v>
       </c>
       <c r="G56">
-        <v>-15.38793988339602</v>
+        <v>-10.84858605085815</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.7907026221404242</v>
       </c>
       <c r="E57">
-        <v>-30.09727508799555</v>
+        <v>-29.02967601950224</v>
       </c>
       <c r="F57">
-        <v>-3.894939258607586</v>
+        <v>-2.763444730262719</v>
       </c>
       <c r="G57">
-        <v>-15.28205539486797</v>
+        <v>-9.620029359052456</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.7983508691234202</v>
       </c>
       <c r="E58">
-        <v>-28.39872826448754</v>
+        <v>-27.32090163744791</v>
       </c>
       <c r="F58">
-        <v>-3.645914964905014</v>
+        <v>-3.932191189150553</v>
       </c>
       <c r="G58">
-        <v>-15.30451910162469</v>
+        <v>-11.29681736414777</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.793105485582294</v>
       </c>
       <c r="E59">
-        <v>-28.96045376582099</v>
+        <v>-25.13102670529269</v>
       </c>
       <c r="F59">
-        <v>-3.886197993807318</v>
+        <v>-3.770233503708138</v>
       </c>
       <c r="G59">
-        <v>-15.04999608420167</v>
+        <v>-10.50746743849165</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.7780190150128627</v>
       </c>
       <c r="E60">
-        <v>-28.99312670578634</v>
+        <v>-23.19718263658313</v>
       </c>
       <c r="F60">
-        <v>-3.781204626437344</v>
+        <v>-3.945125315361947</v>
       </c>
       <c r="G60">
-        <v>-15.31527671935455</v>
+        <v>-11.15729442239519</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.7573175991663087</v>
       </c>
       <c r="E61">
-        <v>-28.10636998255234</v>
+        <v>-26.58972063874743</v>
       </c>
       <c r="F61">
-        <v>-3.938125335215704</v>
+        <v>-4.123963722157031</v>
       </c>
       <c r="G61">
-        <v>-15.34926277986071</v>
+        <v>-10.34175808152343</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.7344692756291111</v>
       </c>
       <c r="E62">
-        <v>-28.07978331165331</v>
+        <v>-23.55973226563722</v>
       </c>
       <c r="F62">
-        <v>-3.857513120413921</v>
+        <v>-3.664740477121843</v>
       </c>
       <c r="G62">
-        <v>-15.04062061923446</v>
+        <v>-10.10470646818391</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.7142847153585032</v>
       </c>
       <c r="E63">
-        <v>-27.4204329676625</v>
+        <v>-22.16894279992749</v>
       </c>
       <c r="F63">
-        <v>-3.620378498871511</v>
+        <v>-3.987058680590953</v>
       </c>
       <c r="G63">
-        <v>-15.47235051828358</v>
+        <v>-9.939761847235266</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.7011192136026166</v>
       </c>
       <c r="E64">
-        <v>-28.00837833350036</v>
+        <v>-25.21992065006326</v>
       </c>
       <c r="F64">
-        <v>-4.058923295768806</v>
+        <v>-3.80462209395599</v>
       </c>
       <c r="G64">
-        <v>-15.81989489954181</v>
+        <v>-11.83432415899492</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.6969773359410292</v>
       </c>
       <c r="E65">
-        <v>-28.5523205174057</v>
+        <v>-24.27598741400842</v>
       </c>
       <c r="F65">
-        <v>-3.858325561548542</v>
+        <v>-3.823810274827454</v>
       </c>
       <c r="G65">
-        <v>-15.49972872989336</v>
+        <v>-11.89417882234494</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.7054502488052999</v>
       </c>
       <c r="E66">
-        <v>-26.91031395612045</v>
+        <v>-25.82996044058455</v>
       </c>
       <c r="F66">
-        <v>-3.891124111057293</v>
+        <v>-4.208617554455016</v>
       </c>
       <c r="G66">
-        <v>-15.79690481604434</v>
+        <v>-10.55529157935196</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.7288345564754043</v>
       </c>
       <c r="E67">
-        <v>-27.00028567770485</v>
+        <v>-24.08105472187424</v>
       </c>
       <c r="F67">
-        <v>-4.164598448535377</v>
+        <v>-4.310907535827334</v>
       </c>
       <c r="G67">
-        <v>-15.56341038388678</v>
+        <v>-10.97327112750372</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.7669277016286551</v>
       </c>
       <c r="E68">
-        <v>-28.26041055439726</v>
+        <v>-25.16739488004829</v>
       </c>
       <c r="F68">
-        <v>-4.018884834667624</v>
+        <v>-4.296879860681329</v>
       </c>
       <c r="G68">
-        <v>-15.10842059187873</v>
+        <v>-10.59683230477873</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.822072296140563</v>
       </c>
       <c r="E69">
-        <v>-27.71089834746249</v>
+        <v>-22.74559415159023</v>
       </c>
       <c r="F69">
-        <v>-4.098082008233962</v>
+        <v>-4.347057207053155</v>
       </c>
       <c r="G69">
-        <v>-15.61526842448669</v>
+        <v>-10.93221374172568</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.8945625904341097</v>
       </c>
       <c r="E70">
-        <v>-27.9832498312318</v>
+        <v>-24.61381157498063</v>
       </c>
       <c r="F70">
-        <v>-4.333120594997288</v>
+        <v>-4.07638919645723</v>
       </c>
       <c r="G70">
-        <v>-15.48816333905191</v>
+        <v>-10.26674111960354</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.9818329027996141</v>
       </c>
       <c r="E71">
-        <v>-27.73666083609213</v>
+        <v>-23.71583329315563</v>
       </c>
       <c r="F71">
-        <v>-4.039745408985792</v>
+        <v>-5.035875049767346</v>
       </c>
       <c r="G71">
-        <v>-15.7782200970207</v>
+        <v>-12.06215590300756</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>1.0822951775679</v>
       </c>
       <c r="E72">
-        <v>-27.61751215647631</v>
+        <v>-23.92272115667005</v>
       </c>
       <c r="F72">
-        <v>-4.251634174530182</v>
+        <v>-3.977143097854386</v>
       </c>
       <c r="G72">
-        <v>-15.30382057651591</v>
+        <v>-11.20372482358347</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.191350539455586</v>
       </c>
       <c r="E73">
-        <v>-27.56615926122933</v>
+        <v>-23.72239052351873</v>
       </c>
       <c r="F73">
-        <v>-4.530089267112323</v>
+        <v>-3.659933137815527</v>
       </c>
       <c r="G73">
-        <v>-15.46356267514959</v>
+        <v>-10.36144258529993</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.303129346732363</v>
       </c>
       <c r="E74">
-        <v>-28.20469673868089</v>
+        <v>-23.32930539423092</v>
       </c>
       <c r="F74">
-        <v>-4.544808229890418</v>
+        <v>-4.384697145545404</v>
       </c>
       <c r="G74">
-        <v>-14.9275952839782</v>
+        <v>-10.52099763811065</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.41366053138939</v>
       </c>
       <c r="E75">
-        <v>-27.68335616854784</v>
+        <v>-21.78379608557513</v>
       </c>
       <c r="F75">
-        <v>-4.500461296846281</v>
+        <v>-5.149707871704345</v>
       </c>
       <c r="G75">
-        <v>-14.78580792907676</v>
+        <v>-11.10024379111693</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.517220450893984</v>
       </c>
       <c r="E76">
-        <v>-28.73225943210048</v>
+        <v>-25.1057034786418</v>
       </c>
       <c r="F76">
-        <v>-4.757941788284342</v>
+        <v>-4.540373061474229</v>
       </c>
       <c r="G76">
-        <v>-14.99248859763899</v>
+        <v>-10.75349063024258</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.608254262642104</v>
       </c>
       <c r="E77">
-        <v>-27.72379091296233</v>
+        <v>-25.29531521381696</v>
       </c>
       <c r="F77">
-        <v>-4.700573625203464</v>
+        <v>-4.597539302050889</v>
       </c>
       <c r="G77">
-        <v>-14.74083085738022</v>
+        <v>-10.47576565440759</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.683364247016675</v>
       </c>
       <c r="E78">
-        <v>-28.07145997642721</v>
+        <v>-25.46150568142446</v>
       </c>
       <c r="F78">
-        <v>-4.725202627747421</v>
+        <v>-4.912957298846429</v>
       </c>
       <c r="G78">
-        <v>-14.44297941993922</v>
+        <v>-9.641081118136681</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.738348237697558</v>
       </c>
       <c r="E79">
-        <v>-28.85450105946353</v>
+        <v>-25.83668975295994</v>
       </c>
       <c r="F79">
-        <v>-4.572160414755972</v>
+        <v>-4.747781522983841</v>
       </c>
       <c r="G79">
-        <v>-14.70067559526163</v>
+        <v>-9.556562890519087</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.770555507829672</v>
       </c>
       <c r="E80">
-        <v>-29.51381064718828</v>
+        <v>-26.43244673646104</v>
       </c>
       <c r="F80">
-        <v>-5.200219380024328</v>
+        <v>-4.455769907765538</v>
       </c>
       <c r="G80">
-        <v>-14.09645634197985</v>
+        <v>-9.19361454086663</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.7784857329057</v>
       </c>
       <c r="E81">
-        <v>-29.94260958673758</v>
+        <v>-26.74589865032397</v>
       </c>
       <c r="F81">
-        <v>-4.925650701758676</v>
+        <v>-5.013150453586706</v>
       </c>
       <c r="G81">
-        <v>-13.69472329606207</v>
+        <v>-9.723036983506878</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.759962212248852</v>
       </c>
       <c r="E82">
-        <v>-29.00751819618271</v>
+        <v>-26.67020520728576</v>
       </c>
       <c r="F82">
-        <v>-5.068459007124555</v>
+        <v>-4.928307368431826</v>
       </c>
       <c r="G82">
-        <v>-14.68949257242997</v>
+        <v>-10.83204656534395</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.714028465292794</v>
       </c>
       <c r="E83">
-        <v>-30.38633437661616</v>
+        <v>-29.89176614481646</v>
       </c>
       <c r="F83">
-        <v>-5.202928308992687</v>
+        <v>-4.745451099729271</v>
       </c>
       <c r="G83">
-        <v>-13.76699416045713</v>
+        <v>-10.70304784786071</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.637889679136602</v>
       </c>
       <c r="E84">
-        <v>-32.37416238397115</v>
+        <v>-28.2586082217422</v>
       </c>
       <c r="F84">
-        <v>-4.956943938794802</v>
+        <v>-4.694258597865649</v>
       </c>
       <c r="G84">
-        <v>-14.15231517686398</v>
+        <v>-10.67212404197838</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.527958679562603</v>
       </c>
       <c r="E85">
-        <v>-32.1286466371713</v>
+        <v>-29.91527571762728</v>
       </c>
       <c r="F85">
-        <v>-4.730673539832306</v>
+        <v>-3.755185130099632</v>
       </c>
       <c r="G85">
-        <v>-14.30550405060267</v>
+        <v>-10.10458066745342</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.381059304703238</v>
       </c>
       <c r="E86">
-        <v>-32.71832640855411</v>
+        <v>-28.99308142104626</v>
       </c>
       <c r="F86">
-        <v>-5.016368544006879</v>
+        <v>-5.032019517716209</v>
       </c>
       <c r="G86">
-        <v>-14.47520923603679</v>
+        <v>-9.957744730604588</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.190367065958339</v>
       </c>
       <c r="E87">
-        <v>-34.00199029313838</v>
+        <v>-31.19891922407852</v>
       </c>
       <c r="F87">
-        <v>-5.191048930920976</v>
+        <v>-4.903291149791544</v>
       </c>
       <c r="G87">
-        <v>-13.62009201269751</v>
+        <v>-10.74222484377245</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.9511124169971775</v>
       </c>
       <c r="E88">
-        <v>-33.9088961887257</v>
+        <v>-32.60775013023481</v>
       </c>
       <c r="F88">
-        <v>-5.090709283383521</v>
+        <v>-4.397215548953995</v>
       </c>
       <c r="G88">
-        <v>-14.02090472695538</v>
+        <v>-10.88301572446657</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.6583235221186903</v>
       </c>
       <c r="E89">
-        <v>-35.58333568085387</v>
+        <v>-32.59612327322012</v>
       </c>
       <c r="F89">
-        <v>-5.095359043951252</v>
+        <v>-4.107499515460122</v>
       </c>
       <c r="G89">
-        <v>-13.62474663972572</v>
+        <v>-9.46206998919167</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.3043838663992135</v>
       </c>
       <c r="E90">
-        <v>-36.76230803909183</v>
+        <v>-33.0993590042705</v>
       </c>
       <c r="F90">
-        <v>-5.330851362459351</v>
+        <v>-4.986701772945909</v>
       </c>
       <c r="G90">
-        <v>-13.51548870529315</v>
+        <v>-9.642080902889541</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.1107601618138259</v>
       </c>
       <c r="E91">
-        <v>-37.74680281683337</v>
+        <v>-35.95242216213803</v>
       </c>
       <c r="F91">
-        <v>-5.300399865117281</v>
+        <v>-4.331910643677892</v>
       </c>
       <c r="G91">
-        <v>-13.42049260104377</v>
+        <v>-10.55442752696621</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.5896041889100574</v>
       </c>
       <c r="E92">
-        <v>-39.08305134159471</v>
+        <v>-37.22451805986972</v>
       </c>
       <c r="F92">
-        <v>-5.161474014803102</v>
+        <v>-4.360258187711301</v>
       </c>
       <c r="G92">
-        <v>-13.88564411258461</v>
+        <v>-10.76688178694894</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.133942128058044</v>
       </c>
       <c r="E93">
-        <v>-39.36143475274224</v>
+        <v>-39.58394585158313</v>
       </c>
       <c r="F93">
-        <v>-5.282354328063807</v>
+        <v>-4.73716277482082</v>
       </c>
       <c r="G93">
-        <v>-13.52760861251243</v>
+        <v>-10.31659793542497</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.733985231746594</v>
       </c>
       <c r="E94">
-        <v>-40.94718408143019</v>
+        <v>-42.9200228398198</v>
       </c>
       <c r="F94">
-        <v>-5.451867082575825</v>
+        <v>-4.013926251446382</v>
       </c>
       <c r="G94">
-        <v>-13.61965502068632</v>
+        <v>-11.17180785403935</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.385480795079902</v>
       </c>
       <c r="E95">
-        <v>-42.53398401608793</v>
+        <v>-41.44102775738867</v>
       </c>
       <c r="F95">
-        <v>-5.254828727400511</v>
+        <v>-4.463910156170897</v>
       </c>
       <c r="G95">
-        <v>-14.34156747843472</v>
+        <v>-10.71217833245802</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.086840879321664</v>
       </c>
       <c r="E96">
-        <v>-44.71333251041232</v>
+        <v>-44.17519809442182</v>
       </c>
       <c r="F96">
-        <v>-5.562435886621104</v>
+        <v>-4.28396157152909</v>
       </c>
       <c r="G96">
-        <v>-14.57002822609983</v>
+        <v>-9.020105538607888</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.815146526967613</v>
       </c>
       <c r="E97">
-        <v>-45.45164811991188</v>
+        <v>-44.13159568243897</v>
       </c>
       <c r="F97">
-        <v>-5.634737604631619</v>
+        <v>-4.319834094219709</v>
       </c>
       <c r="G97">
-        <v>-14.77340331494111</v>
+        <v>-10.38481834735273</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.577859413046794</v>
       </c>
       <c r="E98">
-        <v>-47.91905058162718</v>
+        <v>-46.3335186196916</v>
       </c>
       <c r="F98">
-        <v>-5.680167000668957</v>
+        <v>-4.899734938158425</v>
       </c>
       <c r="G98">
-        <v>-15.00230105461739</v>
+        <v>-12.38600339929569</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.341983670134424</v>
       </c>
       <c r="E99">
-        <v>-48.66700731228908</v>
+        <v>-48.85584241417193</v>
       </c>
       <c r="F99">
-        <v>-5.927179987858921</v>
+        <v>-4.350817716749366</v>
       </c>
       <c r="G99">
-        <v>-14.74947303651048</v>
+        <v>-11.24056788489002</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.123090504370387</v>
       </c>
       <c r="E100">
-        <v>-50.56722519725468</v>
+        <v>-50.36158379621087</v>
       </c>
       <c r="F100">
-        <v>-5.728637112063939</v>
+        <v>-3.981071480377634</v>
       </c>
       <c r="G100">
-        <v>-14.76341705432189</v>
+        <v>-11.20613490073606</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.857663171972217</v>
       </c>
       <c r="E101">
-        <v>-52.0904351677782</v>
+        <v>-50.79861776574311</v>
       </c>
       <c r="F101">
-        <v>-5.686981687223093</v>
+        <v>-3.592747581764839</v>
       </c>
       <c r="G101">
-        <v>-15.7111136836669</v>
+        <v>-10.9919161199809</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.622749483309491</v>
       </c>
       <c r="E102">
-        <v>-54.21071764350205</v>
+        <v>-53.8287068974</v>
       </c>
       <c r="F102">
-        <v>-5.939266831405555</v>
+        <v>-3.754159680519385</v>
       </c>
       <c r="G102">
-        <v>-15.62236954466843</v>
+        <v>-11.55163667539655</v>
       </c>
     </row>
   </sheetData>
